--- a/artfynd/A 23862-2026 artfynd.xlsx
+++ b/artfynd/A 23862-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126512786</v>
+        <v>126512835</v>
       </c>
       <c r="B2" t="n">
-        <v>80018</v>
+        <v>80336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -763,17 +763,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126512804</v>
+        <v>126512786</v>
       </c>
       <c r="B3" t="n">
-        <v>80043</v>
+        <v>80367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -910,7 +910,7 @@
         <v>126512761</v>
       </c>
       <c r="B4" t="n">
-        <v>80112</v>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>126512734</v>
       </c>
       <c r="B5" t="n">
-        <v>80118</v>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126512835</v>
+        <v>124576085</v>
       </c>
       <c r="B6" t="n">
-        <v>79987</v>
+        <v>56766</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,40 +1150,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100077</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gravendal, Dlr</t>
+          <t>Sävälven, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472934</v>
+        <v>472643</v>
       </c>
       <c r="R6" t="n">
-        <v>6656400</v>
+        <v>6656345</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,12 +1212,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,37 +1236,287 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Å</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Rock (&gt; 200 mm) # Inne i vägtrumman</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Sebastian Fall</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Fall</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124576129</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sävälven, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>472790</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6656286</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Å</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Fall</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Fall</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126512804</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gravendal, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>472934</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6656400</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Anton Björk</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Anton Björk</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
